--- a/etf_holdings/2026-09-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,7 +990,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,39 +1005,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>52000</v>
+        <v>55000</v>
       </c>
       <c r="K10" t="n">
-        <v>62000</v>
+        <v>65000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1046,14 +1046,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,60 +1063,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1004000</v>
+        <v>2750000</v>
       </c>
       <c r="K11" t="n">
-        <v>139000</v>
+        <v>2830000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-865,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,55 +1131,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>15.41%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>15.25%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2652000</v>
+        <v>9700000</v>
       </c>
       <c r="K12" t="n">
-        <v>297000</v>
+        <v>9600000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-2,355,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,60 +1189,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1000</v>
+        <v>2307000</v>
       </c>
       <c r="K13" t="n">
-        <v>17000</v>
+        <v>2180000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>-127,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,60 +1252,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>58000</v>
+        <v>1000000</v>
       </c>
       <c r="K14" t="n">
-        <v>71000</v>
+        <v>770000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>-230,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,55 +1320,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17000</v>
+        <v>2600000</v>
       </c>
       <c r="K15" t="n">
-        <v>38000</v>
+        <v>3500000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1383,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>107000</v>
+        <v>620000</v>
       </c>
       <c r="K16" t="n">
-        <v>210000</v>
+        <v>645000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>103,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1475,80 +1475,773 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1074000</v>
+        <v>1300000</v>
       </c>
       <c r="K17" t="n">
-        <v>1104000</v>
+        <v>1500000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-20_00992A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-40,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-1,000,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>762000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>840000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>78,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>+0.51%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>52000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>62000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>富邦金融控股</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>富邦金融控股</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.28%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1004000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>139000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-865,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>中國信託金融控股</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>中國信託金融控股</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.64%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2652000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>297000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-2,355,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>+0.98%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>奇鋐科技</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>奇鋐科技</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2.32%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+0.52%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>71000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>17000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>38000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>21,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+1.58%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>107000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>103,000</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1104000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-20_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>00405A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>6805</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2.28%</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>3.43%</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>+1.15%</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J29" t="n">
         <v>271000</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K29" t="n">
         <v>391000</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>120,000</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2026-09-20_00405A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,7 +801,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>280000</v>
+        <v>1000</v>
       </c>
       <c r="K7" t="n">
-        <v>380000</v>
+        <v>871000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-20_00982A_full_holdings.xlsx</t>
+          <t>2026-09-20_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -874,53 +874,53 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2040000</v>
+        <v>250000</v>
       </c>
       <c r="K8" t="n">
-        <v>2041000</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-249,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-20_00982A_full_holdings.xlsx</t>
+          <t>2026-09-20_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -942,43 +942,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>141000</v>
+        <v>280000</v>
       </c>
       <c r="K9" t="n">
-        <v>143000</v>
+        <v>380000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,55 +1005,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>55000</v>
+        <v>2040000</v>
       </c>
       <c r="K10" t="n">
-        <v>65000</v>
+        <v>2041000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-20_00403A_full_holdings.xlsx</t>
+          <t>2026-09-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1068,48 +1068,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2750000</v>
+        <v>141000</v>
       </c>
       <c r="K11" t="n">
-        <v>2830000</v>
+        <v>143000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-20_00403A_full_holdings.xlsx</t>
+          <t>2026-09-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1126,48 +1126,48 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>15.41%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.25%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>9700000</v>
+        <v>55000</v>
       </c>
       <c r="K12" t="n">
-        <v>9600000</v>
+        <v>65000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1189,48 +1189,48 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2307000</v>
+        <v>2750000</v>
       </c>
       <c r="K13" t="n">
-        <v>2180000</v>
+        <v>2830000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-127,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1257,43 +1257,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>15.41%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>15.25%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1000000</v>
+        <v>9700000</v>
       </c>
       <c r="K14" t="n">
-        <v>770000</v>
+        <v>9600000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-230,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1315,48 +1315,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2600000</v>
+        <v>2307000</v>
       </c>
       <c r="K15" t="n">
-        <v>3500000</v>
+        <v>2180000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>-127,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1378,48 +1378,48 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>620000</v>
+        <v>1000000</v>
       </c>
       <c r="K16" t="n">
-        <v>645000</v>
+        <v>770000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>-230,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1446,43 +1446,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1300000</v>
+        <v>2600000</v>
       </c>
       <c r="K17" t="n">
-        <v>1500000</v>
+        <v>3500000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1504,48 +1504,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>80000</v>
+        <v>620000</v>
       </c>
       <c r="K18" t="n">
-        <v>40000</v>
+        <v>645000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1567,48 +1567,48 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2800000</v>
+        <v>1300000</v>
       </c>
       <c r="K19" t="n">
-        <v>1800000</v>
+        <v>1500000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-1,000,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1630,48 +1630,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>762000</v>
+        <v>80000</v>
       </c>
       <c r="K20" t="n">
-        <v>840000</v>
+        <v>40000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>78,000</t>
+          <t>-40,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1683,7 +1683,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,60 +1693,60 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>52000</v>
+        <v>2800000</v>
       </c>
       <c r="K21" t="n">
-        <v>62000</v>
+        <v>1800000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-1,000,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,53 +1756,53 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1004000</v>
+        <v>762000</v>
       </c>
       <c r="K22" t="n">
-        <v>139000</v>
+        <v>840000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-865,000</t>
+          <t>78,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+          <t>2026-09-20_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1819,48 +1819,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2652000</v>
+        <v>52000</v>
       </c>
       <c r="K23" t="n">
-        <v>297000</v>
+        <v>62000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-2,355,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1882,48 +1882,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1000</v>
+        <v>1004000</v>
       </c>
       <c r="K24" t="n">
-        <v>17000</v>
+        <v>139000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>-865,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1945,48 +1945,48 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>58000</v>
+        <v>2652000</v>
       </c>
       <c r="K25" t="n">
-        <v>71000</v>
+        <v>297000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>-2,355,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2038,18 +2038,18 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="J26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K26" t="n">
         <v>17000</v>
       </c>
-      <c r="K26" t="n">
-        <v>38000</v>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2076,43 +2076,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>107000</v>
+        <v>58000</v>
       </c>
       <c r="K27" t="n">
-        <v>210000</v>
+        <v>71000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>103,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2139,109 +2139,280 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1074000</v>
+        <v>17000</v>
       </c>
       <c r="K28" t="n">
-        <v>1104000</v>
+        <v>38000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-20_00992A_full_holdings.xlsx</t>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+1.58%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>107000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>103,000</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1104000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-20_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6920</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>LASERTEC CORP</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>22600</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-20_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>00405A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>6805</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2.28%</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>3.43%</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>+1.15%</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J32" t="n">
         <v>271000</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K32" t="n">
         <v>391000</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>120,000</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2026-09-20_00405A_full_holdings.xlsx</t>
         </is>
